--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/updateWorkoutSessionSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/updateWorkoutSessionSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="123">
-  <si>
-    <t>Statement: updateWorkoutSessionSchema – validate partial update for a workout session.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="130">
+  <si>
+    <t>Statement: updateWorkoutSessionSchema – Validates a partial update for a workout session using Zod safeParse. All fields are optional; an empty object is valid. Returns { success: true, data } when every supplied field satisfies its constraint. Returns { success: false, error } with a path pointing to the offending field when any supplied field violates its constraint. Field constraints when present: date must be in YYYY-MM-DD format. duration must be an integer in the range 0–180 inclusive. notes accepts an empty string, a whitespace-only string trimmed to "", or a non-empty string up to 1024 characters after trimming; surrounding whitespace trimmed.</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>All optional. same constraints as create.</t>
+    <t>Input is passed directly to updateWorkoutSessionSchema.safeParse(). All fields are optional. When present, each field is subject to the same constraints as in createWorkoutSessionSchema. date: YYYY-MM-DD format. duration: integer, 0 ≤ duration ≤ 180. notes: when present, trimmed before length check, max 1024 characters after trim, whitespace-only trimmed to "".</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: true, data } OR { success: false, error }</t>
+    <t>Output: { success: boolean, data?: UpdateWorkoutSessionInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match constraints.</t>
+    <t>On success: parsed data contains only the supplied fields with notes trimmed. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,46 +64,37 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Empty object</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
-    <t>Date only</t>
-  </si>
-  <si>
-    <t>Valid format</t>
-  </si>
-  <si>
-    <t>Invalid format</t>
-  </si>
-  <si>
-    <t>Duration only</t>
-  </si>
-  <si>
-    <t>0-180</t>
-  </si>
-  <si>
-    <t>Notes only</t>
-  </si>
-  <si>
-    <t>0-1024 chars</t>
-  </si>
-  <si>
-    <t>Date format</t>
-  </si>
-  <si>
-    <t>Invalid format string</t>
-  </si>
-  <si>
-    <t>Notes whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Whitespace only</t>
+    <t>Empty input</t>
+  </si>
+  <si>
+    <t>Empty object {} → success: true, parsed data is {}</t>
+  </si>
+  <si>
+    <t>date value</t>
+  </si>
+  <si>
+    <t>date: "2024-06-15" (valid YYYY-MM-DD) → success: true, parsed date is "2024-06-15"</t>
+  </si>
+  <si>
+    <t>date: "01/01/2024" (MM/DD/YYYY, wrong format) → success: false, error path contains "date"</t>
+  </si>
+  <si>
+    <t>duration value</t>
+  </si>
+  <si>
+    <t>duration: 45 (within range 0–180) → success: true, parsed duration is 45</t>
+  </si>
+  <si>
+    <t>notes value</t>
+  </si>
+  <si>
+    <t>notes: "Updated notes" (valid length) → success: true, parsed notes matches input</t>
+  </si>
+  <si>
+    <t>notes content</t>
+  </si>
+  <si>
+    <t>notes: "  updated notes  " (surrounding whitespace) → success: true, parsed notes is "updated notes"; notes: "     " (whitespace-only) → success: true, parsed notes is ""</t>
   </si>
   <si>
     <t>No TC</t>
@@ -124,7 +115,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>success: true</t>
+    <t>empty object {}</t>
+  </si>
+  <si>
+    <t>success: true, parsed data is {}</t>
   </si>
   <si>
     <t>Passed</t>
@@ -133,37 +127,49 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>{date: "2024-06-15"}</t>
+    <t>object with only date: "2024-06-15"</t>
+  </si>
+  <si>
+    <t>success: true, parsed date is "2024-06-15"</t>
+  </si>
+  <si>
+    <t>object with only date: "01/01/2024" (MM/DD/YYYY, wrong format)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "date"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>{duration: 45}</t>
+    <t>object with only duration: 45</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 45</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>{notes: "Updated notes"}</t>
+    <t>object with only notes: "Updated notes"</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "Updated notes"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>{date: "01/01/2024"}</t>
-  </si>
-  <si>
-    <t>success: false</t>
-  </si>
-  <si>
-    <t>EC-6</t>
-  </si>
-  <si>
-    <t>notes="     "</t>
-  </si>
-  <si>
-    <t>notes="  updated notes  "</t>
+    <t>object with only notes: "     " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is ""</t>
+  </si>
+  <si>
+    <t>object with only notes: "  updated notes  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "updated notes"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -172,121 +178,151 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Duration range</t>
-  </si>
-  <si>
-    <t>-1 (Below Min)</t>
-  </si>
-  <si>
-    <t>0 (At Min)</t>
-  </si>
-  <si>
-    <t>1 (Above Min)</t>
-  </si>
-  <si>
-    <t>179 (Below Max)</t>
-  </si>
-  <si>
-    <t>180 (At Max)</t>
-  </si>
-  <si>
-    <t>181 (Above Max)</t>
-  </si>
-  <si>
-    <t>Notes length</t>
-  </si>
-  <si>
-    <t>0 chars (At Min)</t>
-  </si>
-  <si>
-    <t>1 char (Above Min)</t>
-  </si>
-  <si>
-    <t>1023 chars (Below Max)</t>
-  </si>
-  <si>
-    <t>1024 chars (At Max)</t>
-  </si>
-  <si>
-    <t>1025 chars (Above Max)</t>
-  </si>
-  <si>
-    <t>1024 chars padded</t>
+    <t>duration range</t>
+  </si>
+  <si>
+    <t>duration: -1 (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>duration: 0 (min): at minimum → success: true, parsed duration is 0</t>
+  </si>
+  <si>
+    <t>duration: 1 (min + 1): above minimum → success: true, parsed duration is 1</t>
+  </si>
+  <si>
+    <t>duration: 179 (max - 1): below maximum → success: true, parsed duration is 179</t>
+  </si>
+  <si>
+    <t>duration: 180 (max): at maximum → success: true, parsed duration is 180</t>
+  </si>
+  <si>
+    <t>duration: 181 (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>notes length</t>
+  </si>
+  <si>
+    <t>notes: "" (length 0, min): at minimum → success: true, parsed notes is ""</t>
+  </si>
+  <si>
+    <t>notes: "A" (length 1, min + 1): above minimum → success: true, parsed notes is "A"</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1023) (max - 1): below maximum → success: true</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1024) (max): at maximum → success: true</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1025) (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>notes whitespace + trim</t>
+  </si>
+  <si>
+    <t>notes: " " + "A".repeat(1024) + " " (1024 real characters after trim, at maximum) → success: true, parsed notes is "A".repeat(1024)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Dur -1</t>
-  </si>
-  <si>
-    <t>duration=-1</t>
-  </si>
-  <si>
-    <t>BVA-1 Dur 0</t>
-  </si>
-  <si>
-    <t>duration=0</t>
-  </si>
-  <si>
-    <t>BVA-1 Dur 1</t>
-  </si>
-  <si>
-    <t>duration=1</t>
-  </si>
-  <si>
-    <t>BVA-1 Dur 179</t>
-  </si>
-  <si>
-    <t>duration=179</t>
-  </si>
-  <si>
-    <t>BVA-1 Dur 180</t>
-  </si>
-  <si>
-    <t>duration=180</t>
-  </si>
-  <si>
-    <t>BVA-1 Dur 181</t>
-  </si>
-  <si>
-    <t>duration=181</t>
-  </si>
-  <si>
-    <t>BVA-2 Notes 0ch</t>
-  </si>
-  <si>
-    <t>notes len 0</t>
-  </si>
-  <si>
-    <t>BVA-2 Notes 1ch</t>
-  </si>
-  <si>
-    <t>notes len 1</t>
-  </si>
-  <si>
-    <t>BVA-2 Notes 1023ch</t>
-  </si>
-  <si>
-    <t>notes len 1023</t>
-  </si>
-  <si>
-    <t>BVA-2 Notes 1024ch</t>
-  </si>
-  <si>
-    <t>notes len 1024</t>
-  </si>
-  <si>
-    <t>BVA-2 Notes 1025ch</t>
-  </si>
-  <si>
-    <t>notes len 1025</t>
-  </si>
-  <si>
-    <t>BVA-3 Notes padded</t>
-  </si>
-  <si>
-    <t>notes=" " + "A".repeat(1024) + " "</t>
+    <t>BVA-1  (dur=-1)</t>
+  </si>
+  <si>
+    <t>object with only duration: -1</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "duration"</t>
+  </si>
+  <si>
+    <t>BVA-2  (dur=0)</t>
+  </si>
+  <si>
+    <t>object with only duration: 0</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 0</t>
+  </si>
+  <si>
+    <t>BVA-3  (dur=1)</t>
+  </si>
+  <si>
+    <t>object with only duration: 1</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 1</t>
+  </si>
+  <si>
+    <t>BVA-4  (dur=179)</t>
+  </si>
+  <si>
+    <t>object with only duration: 179</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 179</t>
+  </si>
+  <si>
+    <t>BVA-5  (dur=180)</t>
+  </si>
+  <si>
+    <t>object with only duration: 180</t>
+  </si>
+  <si>
+    <t>success: true, parsed duration is 180</t>
+  </si>
+  <si>
+    <t>BVA-6  (dur=181)</t>
+  </si>
+  <si>
+    <t>object with only duration: 181</t>
+  </si>
+  <si>
+    <t>BVA-7  (notes=0)</t>
+  </si>
+  <si>
+    <t>object with only notes: "" (0 characters)</t>
+  </si>
+  <si>
+    <t>BVA-8  (notes=1)</t>
+  </si>
+  <si>
+    <t>object with only notes: "A" (1 character)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "A"</t>
+  </si>
+  <si>
+    <t>BVA-9  (notes=1023)</t>
+  </si>
+  <si>
+    <t>object with only notes: "A".repeat(1023) (1023 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "A".repeat(1023)</t>
+  </si>
+  <si>
+    <t>BVA-10 (notes=1024)</t>
+  </si>
+  <si>
+    <t>object with only notes: "A".repeat(1024) (1024 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed notes is "A".repeat(1024)</t>
+  </si>
+  <si>
+    <t>BVA-11 (notes=1025)</t>
+  </si>
+  <si>
+    <t>object with only notes: "A".repeat(1025) (1025 characters)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "notes"</t>
+  </si>
+  <si>
+    <t>BVA-12 (pad→1024)</t>
+  </si>
+  <si>
+    <t>object with only notes: " " + "A".repeat(1024) + " " (1024 real characters after trim)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -295,55 +331,40 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Empty update object {}</t>
-  </si>
-  <si>
-    <t>{date: "2024-06-15"} (Valid date)</t>
-  </si>
-  <si>
-    <t>{duration: 45} (Valid duration)</t>
-  </si>
-  <si>
-    <t>{notes: "Updated notes"} (Valid notes)</t>
-  </si>
-  <si>
-    <t>{date: "01/01/2024"} (Wrong format)</t>
-  </si>
-  <si>
-    <t>Notes whitespace only</t>
-  </si>
-  <si>
-    <t>Notes with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>duration=-1 (Below Min)</t>
-  </si>
-  <si>
-    <t>duration=0 (At Min)</t>
-  </si>
-  <si>
-    <t>duration=1 (Above Min)</t>
-  </si>
-  <si>
-    <t>duration=179 (Below Max)</t>
-  </si>
-  <si>
-    <t>duration=180 (At Max)</t>
-  </si>
-  <si>
-    <t>duration=181 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>notes padded with whitespace</t>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
   </si>
   <si>
     <t>Testing</t>
@@ -376,7 +397,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-06</t>
+    <t>SCHEMA-11</t>
   </si>
   <si>
     <t>n/a</t>
@@ -901,7 +922,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -987,24 +1008,10 @@
         <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1027,19 +1034,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1047,16 +1054,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1064,16 +1071,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1081,16 +1088,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1098,16 +1105,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1124,7 +1131,7 @@
         <v>45</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1138,10 +1145,10 @@
         <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1152,13 +1159,13 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1179,13 +1186,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1193,131 +1200,131 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="1">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
+      <c r="A11" s="1">
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
+      <c r="A12" s="1">
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1340,19 +1347,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1360,16 +1367,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1377,16 +1384,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1394,16 +1401,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1411,16 +1418,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1428,16 +1435,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1445,16 +1452,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1462,16 +1469,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1479,16 +1486,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1496,16 +1503,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1513,16 +1520,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1530,16 +1537,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1547,16 +1554,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1580,22 +1587,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1603,19 +1610,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1623,19 +1630,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1643,19 +1650,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1663,19 +1670,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1689,13 +1696,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1709,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1729,13 +1736,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1746,16 +1753,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1766,16 +1773,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,16 +1793,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1806,16 +1813,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1826,16 +1833,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1846,16 +1853,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1866,16 +1873,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1886,16 +1893,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1906,16 +1913,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1926,16 +1933,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1946,16 +1953,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1966,16 +1973,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2003,16 +2010,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2020,39 +2027,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B3" s="1">
         <v>19</v>
@@ -2067,19 +2074,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/updateWorkoutSessionSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/updateWorkoutSessionSchema-bbt-form.xlsx
@@ -397,7 +397,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-11</t>
+    <t>SCHEMA-13</t>
   </si>
   <si>
     <t>n/a</t>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/updateWorkoutSessionSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/updateWorkoutSessionSchema-bbt-form.xlsx
@@ -397,7 +397,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-13</t>
+    <t>SCHEMA-14</t>
   </si>
   <si>
     <t>n/a</t>
